--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123280124</v>
+        <v>123280720</v>
       </c>
       <c r="B2" t="n">
-        <v>90972</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505726</v>
+        <v>505723</v>
       </c>
       <c r="R2" t="n">
-        <v>6573245</v>
+        <v>6573415</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,11 +765,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>4 tickor på samma tall.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -782,21 +778,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123280125</v>
+        <v>123280332</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,50 +807,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505726</v>
+        <v>505716</v>
       </c>
       <c r="R3" t="n">
-        <v>6573245</v>
+        <v>6573177</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -904,19 +881,33 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hack i död trädstam.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123280108</v>
+        <v>123280178</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>90972</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,35 +937,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -982,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505744</v>
+        <v>505688</v>
       </c>
       <c r="R4" t="n">
-        <v>6573212</v>
+        <v>6573291</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,8 +1016,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1044,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123280304</v>
+        <v>123280125</v>
       </c>
       <c r="B5" t="n">
-        <v>39923</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,47 +1072,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101166</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505683</v>
+        <v>505726</v>
       </c>
       <c r="R5" t="n">
-        <v>6573205</v>
+        <v>6573245</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1144,26 +1163,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1181,7 +1180,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123280178</v>
+        <v>123280124</v>
       </c>
       <c r="B6" t="n">
         <v>90972</v>
@@ -1216,22 +1215,26 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505688</v>
+        <v>505726</v>
       </c>
       <c r="R6" t="n">
-        <v>6573291</v>
+        <v>6573245</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1266,6 +1269,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>4 tickor på samma tall.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1291,14 +1299,9 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1446,10 +1449,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123280343</v>
+        <v>123280108</v>
       </c>
       <c r="B8" t="n">
-        <v>8430</v>
+        <v>56688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1462,30 +1465,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1495,10 +1497,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505723</v>
+        <v>505744</v>
       </c>
       <c r="R8" t="n">
-        <v>6573156</v>
+        <v>6573212</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1539,34 +1541,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1583,10 +1559,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123280720</v>
+        <v>123280343</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>8430</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1595,39 +1571,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1638,7 +1611,7 @@
         <v>505723</v>
       </c>
       <c r="R9" t="n">
-        <v>6573415</v>
+        <v>6573156</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1686,6 +1659,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1703,10 +1696,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123280332</v>
+        <v>123280304</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>39923</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1719,29 +1712,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>101166</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1751,10 +1745,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505716</v>
+        <v>505683</v>
       </c>
       <c r="R10" t="n">
-        <v>6573177</v>
+        <v>6573205</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1789,17 +1783,13 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska hack i död trädstam.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1808,14 +1798,24 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1831,6 +1831,400 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123377883</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58156</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>505503</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6572768</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gräve</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123374704</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>505574</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6573159</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gräve</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gamla ringhack i tall.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Arneborn, Camilla Berglund, Anneli Sjöstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123372894</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57629</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>505631</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6573031</v>
+      </c>
+      <c r="S13" t="n">
+        <v>40</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gräve</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,6 +2225,152 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123377543</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90975</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Uggle stenar, Uggle stenar, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>505448</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6572904</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gräve</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Okulärt artbestämd</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anneli Sjöstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anneli Sjöstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123280720</v>
+        <v>123280204</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505723</v>
+        <v>505719</v>
       </c>
       <c r="R2" t="n">
-        <v>6573415</v>
+        <v>6573262</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,19 +761,33 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hack i död trädstam</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead tree stem</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -795,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123280332</v>
+        <v>123280178</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>90975</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,31 +821,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505716</v>
+        <v>505688</v>
       </c>
       <c r="R3" t="n">
-        <v>6573177</v>
+        <v>6573291</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,17 +890,13 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska hack i död trädstam.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,14 +905,24 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -925,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123280178</v>
+        <v>123280304</v>
       </c>
       <c r="B4" t="n">
-        <v>90972</v>
+        <v>39926</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,30 +956,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>101166</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505688</v>
+        <v>505683</v>
       </c>
       <c r="R4" t="n">
-        <v>6573291</v>
+        <v>6573205</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1027,12 +1044,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1042,7 +1059,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1063,7 +1080,7 @@
         <v>123280125</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1180,10 +1197,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123280124</v>
+        <v>123280720</v>
       </c>
       <c r="B6" t="n">
-        <v>90972</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1192,49 +1209,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505726</v>
+        <v>505723</v>
       </c>
       <c r="R6" t="n">
-        <v>6573245</v>
+        <v>6573415</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1269,11 +1287,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>4 tickor på samma tall.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1287,21 +1300,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1319,10 +1317,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123280204</v>
+        <v>123280343</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1331,33 +1329,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1367,10 +1366,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505719</v>
+        <v>505723</v>
       </c>
       <c r="R7" t="n">
-        <v>6573262</v>
+        <v>6573156</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1405,17 +1404,13 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska hack i död trädstam</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1424,14 +1419,24 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Död trädstam</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Dead tree stem</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1452,7 +1457,7 @@
         <v>123280108</v>
       </c>
       <c r="B8" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1559,10 +1564,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123280343</v>
+        <v>123280332</v>
       </c>
       <c r="B9" t="n">
-        <v>8430</v>
+        <v>57497</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1571,34 +1576,33 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1608,10 +1612,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505723</v>
+        <v>505716</v>
       </c>
       <c r="R9" t="n">
-        <v>6573156</v>
+        <v>6573177</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1646,13 +1650,17 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska hack i död trädstam.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1661,24 +1669,14 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1696,10 +1694,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123280304</v>
+        <v>123280124</v>
       </c>
       <c r="B10" t="n">
-        <v>39923</v>
+        <v>90975</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1712,43 +1710,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101166</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505683</v>
+        <v>505726</v>
       </c>
       <c r="R10" t="n">
-        <v>6573205</v>
+        <v>6573245</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1783,6 +1783,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>4 tickor på samma tall.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1800,22 +1805,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1836,7 +1836,7 @@
         <v>123377883</v>
       </c>
       <c r="B11" t="n">
-        <v>58156</v>
+        <v>58159</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123374704</v>
+        <v>123372894</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1971,16 +1971,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103020</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1989,27 +1989,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505574</v>
+        <v>505631</v>
       </c>
       <c r="R12" t="n">
-        <v>6573159</v>
+        <v>6573031</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2038,7 +2035,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2048,12 +2045,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gamla ringhack i tall.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2068,26 +2060,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2098,17 +2070,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Per Arneborn, Camilla Berglund, Anneli Sjöstrand</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123372894</v>
+        <v>123374704</v>
       </c>
       <c r="B13" t="n">
-        <v>57629</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2121,16 +2093,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103020</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2139,24 +2111,27 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505631</v>
+        <v>505574</v>
       </c>
       <c r="R13" t="n">
-        <v>6573031</v>
+        <v>6573159</v>
       </c>
       <c r="S13" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2185,7 +2160,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2195,7 +2170,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gamla ringhack i tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2210,6 +2190,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Arneborn, Camilla Berglund, Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123280204</v>
+        <v>123280332</v>
       </c>
       <c r="B2" t="n">
         <v>57497</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505719</v>
+        <v>505716</v>
       </c>
       <c r="R2" t="n">
-        <v>6573262</v>
+        <v>6573177</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska hack i död trädstam</t>
+          <t>Färska hack i död trädstam.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,12 +782,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Död trädstam</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Dead tree stem</t>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123280178</v>
+        <v>123280204</v>
       </c>
       <c r="B3" t="n">
-        <v>90975</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,30 +821,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -852,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505688</v>
+        <v>505719</v>
       </c>
       <c r="R3" t="n">
-        <v>6573291</v>
+        <v>6573262</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -890,13 +891,17 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hack i död trädstam</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,24 +910,14 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död trädstam</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Dead tree stem</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1077,10 +1072,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123280125</v>
+        <v>123280124</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1089,39 +1084,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1167,6 +1161,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4 tickor på samma tall.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1180,6 +1179,21 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1200,7 +1214,7 @@
         <v>123280720</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1454,10 +1468,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123280108</v>
+        <v>123280178</v>
       </c>
       <c r="B8" t="n">
-        <v>56691</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1466,35 +1480,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1502,10 +1515,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505744</v>
+        <v>505688</v>
       </c>
       <c r="R8" t="n">
-        <v>6573212</v>
+        <v>6573291</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1546,8 +1559,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1564,10 +1603,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123280332</v>
+        <v>123280108</v>
       </c>
       <c r="B9" t="n">
-        <v>57497</v>
+        <v>56691</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1576,25 +1615,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1602,7 +1641,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1612,10 +1651,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505716</v>
+        <v>505744</v>
       </c>
       <c r="R9" t="n">
-        <v>6573177</v>
+        <v>6573212</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1650,11 +1689,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska hack i död trädstam.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1663,21 +1697,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1694,10 +1713,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123280124</v>
+        <v>123280125</v>
       </c>
       <c r="B10" t="n">
-        <v>90975</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1706,38 +1725,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1783,11 +1803,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>4 tickor på samma tall.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1801,21 +1816,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123377883</v>
+        <v>123372894</v>
       </c>
       <c r="B11" t="n">
-        <v>58159</v>
+        <v>57632</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1845,20 +1845,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1878,13 +1878,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505503</v>
+        <v>505631</v>
       </c>
       <c r="R11" t="n">
-        <v>6572768</v>
+        <v>6573031</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1955,10 +1955,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123372894</v>
+        <v>123374704</v>
       </c>
       <c r="B12" t="n">
-        <v>57632</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1971,16 +1971,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103020</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1989,24 +1989,27 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505631</v>
+        <v>505574</v>
       </c>
       <c r="R12" t="n">
-        <v>6573031</v>
+        <v>6573159</v>
       </c>
       <c r="S12" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2035,7 +2038,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2045,7 +2048,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gamla ringhack i tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2060,6 +2068,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2070,17 +2098,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Arneborn, Anneli Sjöstrand, Camilla Berglund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123374704</v>
+        <v>123377883</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>58159</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2089,20 +2117,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103044</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2111,27 +2139,24 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505574</v>
+        <v>505503</v>
       </c>
       <c r="R13" t="n">
-        <v>6573159</v>
+        <v>6572768</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2160,7 +2185,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2170,12 +2195,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gamla ringhack i tall.</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2190,26 +2210,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Per Arneborn, Camilla Berglund, Anneli Sjöstrand</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2230,7 +2230,7 @@
         <v>123377543</v>
       </c>
       <c r="B14" t="n">
-        <v>90975</v>
+        <v>90977</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -1072,10 +1072,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123280124</v>
+        <v>123280720</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1084,49 +1084,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505726</v>
+        <v>505723</v>
       </c>
       <c r="R5" t="n">
-        <v>6573245</v>
+        <v>6573415</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1161,11 +1162,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>4 tickor på samma tall.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1179,21 +1175,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1211,10 +1192,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123280720</v>
+        <v>123280124</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1223,50 +1204,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505723</v>
+        <v>505726</v>
       </c>
       <c r="R6" t="n">
-        <v>6573415</v>
+        <v>6573245</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1301,6 +1281,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>4 tickor på samma tall.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1314,6 +1299,21 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123280332</v>
+        <v>123280343</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>8430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505716</v>
+        <v>505723</v>
       </c>
       <c r="R2" t="n">
-        <v>6573177</v>
+        <v>6573156</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,17 +762,13 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska hack i död trädstam.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,14 +777,24 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -935,10 +942,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123280304</v>
+        <v>123280125</v>
       </c>
       <c r="B4" t="n">
-        <v>39926</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,47 +954,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101166</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505683</v>
+        <v>505726</v>
       </c>
       <c r="R4" t="n">
-        <v>6573205</v>
+        <v>6573245</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1035,26 +1045,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1072,10 +1062,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123280720</v>
+        <v>123280124</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1084,50 +1074,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505723</v>
+        <v>505726</v>
       </c>
       <c r="R5" t="n">
-        <v>6573415</v>
+        <v>6573245</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1162,6 +1151,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4 tickor på samma tall.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1175,6 +1169,21 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1192,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123280124</v>
+        <v>123280178</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>90983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1227,26 +1236,22 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505726</v>
+        <v>505688</v>
       </c>
       <c r="R6" t="n">
-        <v>6573245</v>
+        <v>6573291</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1281,11 +1286,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>4 tickor på samma tall.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1311,9 +1311,14 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1331,10 +1336,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123280343</v>
+        <v>123280332</v>
       </c>
       <c r="B7" t="n">
-        <v>8430</v>
+        <v>57497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1343,34 +1348,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1380,10 +1384,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505723</v>
+        <v>505716</v>
       </c>
       <c r="R7" t="n">
-        <v>6573156</v>
+        <v>6573177</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1418,13 +1422,17 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska hack i död trädstam.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1433,24 +1441,14 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1468,10 +1466,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123280178</v>
+        <v>123280720</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1480,34 +1478,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1515,10 +1518,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505688</v>
+        <v>505723</v>
       </c>
       <c r="R8" t="n">
-        <v>6573291</v>
+        <v>6573415</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1566,26 +1569,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1603,10 +1586,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123280108</v>
+        <v>123280304</v>
       </c>
       <c r="B9" t="n">
-        <v>56691</v>
+        <v>39926</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1615,33 +1598,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>101166</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1651,10 +1635,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505744</v>
+        <v>505683</v>
       </c>
       <c r="R9" t="n">
-        <v>6573212</v>
+        <v>6573205</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1695,8 +1679,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1713,10 +1723,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123280125</v>
+        <v>123280108</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>56691</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1725,50 +1735,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505726</v>
+        <v>505744</v>
       </c>
       <c r="R10" t="n">
-        <v>6573245</v>
+        <v>6573212</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1809,14 +1815,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1833,10 +1833,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123372894</v>
+        <v>123374704</v>
       </c>
       <c r="B11" t="n">
-        <v>57632</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1849,16 +1849,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103020</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1867,24 +1867,27 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505631</v>
+        <v>505574</v>
       </c>
       <c r="R11" t="n">
-        <v>6573031</v>
+        <v>6573159</v>
       </c>
       <c r="S11" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1913,7 +1916,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1923,7 +1926,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gamla ringhack i tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1938,6 +1946,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1948,17 +1976,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Arneborn, Camilla Berglund, Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123374704</v>
+        <v>123372894</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>57632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1971,16 +1999,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103020</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1989,27 +2017,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505574</v>
+        <v>505631</v>
       </c>
       <c r="R12" t="n">
-        <v>6573159</v>
+        <v>6573031</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2038,7 +2063,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2048,12 +2073,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gamla ringhack i tall.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2068,26 +2088,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Per Arneborn, Anneli Sjöstrand, Camilla Berglund</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2230,7 +2230,7 @@
         <v>123377543</v>
       </c>
       <c r="B14" t="n">
-        <v>90977</v>
+        <v>90983</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123280204</v>
+        <v>123280720</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505719</v>
+        <v>505723</v>
       </c>
       <c r="R2" t="n">
-        <v>6573262</v>
+        <v>6573415</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,33 +765,19 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska hack i död trädstam</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Dead tree stem</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123280108</v>
+        <v>123280178</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>91003</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,35 +807,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -853,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505744</v>
+        <v>505688</v>
       </c>
       <c r="R3" t="n">
-        <v>6573212</v>
+        <v>6573291</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,8 +886,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -915,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123280178</v>
+        <v>123280332</v>
       </c>
       <c r="B4" t="n">
-        <v>90986</v>
+        <v>57503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,30 +946,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -962,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505688</v>
+        <v>505716</v>
       </c>
       <c r="R4" t="n">
-        <v>6573291</v>
+        <v>6573177</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,13 +1016,17 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hack i död trädstam.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,24 +1035,14 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1050,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123280124</v>
+        <v>123280343</v>
       </c>
       <c r="B5" t="n">
-        <v>90986</v>
+        <v>8434</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,49 +1072,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505726</v>
+        <v>505723</v>
       </c>
       <c r="R5" t="n">
-        <v>6573245</v>
+        <v>6573156</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1139,11 +1147,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>4 tickor på samma tall.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1161,17 +1164,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1189,10 +1197,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123280304</v>
+        <v>123280108</v>
       </c>
       <c r="B6" t="n">
-        <v>39926</v>
+        <v>56697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1201,34 +1209,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101166</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1238,10 +1245,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505683</v>
+        <v>505744</v>
       </c>
       <c r="R6" t="n">
-        <v>6573205</v>
+        <v>6573212</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1282,34 +1289,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1326,10 +1307,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123280343</v>
+        <v>123280125</v>
       </c>
       <c r="B7" t="n">
-        <v>8430</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1338,47 +1319,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505723</v>
+        <v>505726</v>
       </c>
       <c r="R7" t="n">
-        <v>6573156</v>
+        <v>6573245</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1426,26 +1410,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1463,10 +1427,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123280332</v>
+        <v>123280124</v>
       </c>
       <c r="B8" t="n">
-        <v>57497</v>
+        <v>91003</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1479,42 +1443,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505716</v>
+        <v>505726</v>
       </c>
       <c r="R8" t="n">
-        <v>6573177</v>
+        <v>6573245</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1551,7 +1518,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska hack i död trädstam.</t>
+          <t>4 tickor på samma tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,6 +1527,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1568,14 +1536,19 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1593,10 +1566,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123280720</v>
+        <v>123280304</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>39932</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1605,39 +1578,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>101166</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1645,10 +1615,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505723</v>
+        <v>505683</v>
       </c>
       <c r="R9" t="n">
-        <v>6573415</v>
+        <v>6573205</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1696,6 +1666,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1713,10 +1703,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123280125</v>
+        <v>123280204</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1725,50 +1715,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505726</v>
+        <v>505719</v>
       </c>
       <c r="R10" t="n">
-        <v>6573245</v>
+        <v>6573262</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1803,19 +1789,33 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska hack i död trädstam</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Dead tree stem</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123372894</v>
+        <v>123377883</v>
       </c>
       <c r="B11" t="n">
-        <v>57632</v>
+        <v>58165</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1845,20 +1845,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103020</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1878,13 +1878,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505631</v>
+        <v>505503</v>
       </c>
       <c r="R11" t="n">
-        <v>6573031</v>
+        <v>6572768</v>
       </c>
       <c r="S11" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1955,10 +1955,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123377883</v>
+        <v>123374704</v>
       </c>
       <c r="B12" t="n">
-        <v>58159</v>
+        <v>57487</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1967,20 +1967,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1989,24 +1989,27 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505503</v>
+        <v>505574</v>
       </c>
       <c r="R12" t="n">
-        <v>6572768</v>
+        <v>6573159</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2035,7 +2038,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2045,7 +2048,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gamla ringhack i tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2060,6 +2068,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2070,17 +2098,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Arneborn, Camilla Berglund, Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123374704</v>
+        <v>123372894</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>57638</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2093,16 +2121,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103020</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2111,27 +2139,24 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505574</v>
+        <v>505631</v>
       </c>
       <c r="R13" t="n">
-        <v>6573159</v>
+        <v>6573031</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2160,7 +2185,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2170,12 +2195,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gamla ringhack i tall.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2190,26 +2210,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Per Arneborn, Camilla Berglund, Anneli Sjöstrand</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2230,7 +2230,7 @@
         <v>123377543</v>
       </c>
       <c r="B14" t="n">
-        <v>90986</v>
+        <v>91003</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123280720</v>
+        <v>123280304</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>39935</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>101166</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505723</v>
+        <v>505683</v>
       </c>
       <c r="R2" t="n">
-        <v>6573415</v>
+        <v>6573205</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -778,6 +775,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -795,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123280178</v>
+        <v>123280108</v>
       </c>
       <c r="B3" t="n">
-        <v>91003</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +824,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505688</v>
+        <v>505744</v>
       </c>
       <c r="R3" t="n">
-        <v>6573291</v>
+        <v>6573212</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,34 +904,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -930,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123280332</v>
+        <v>123280125</v>
       </c>
       <c r="B4" t="n">
-        <v>57503</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,46 +934,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505716</v>
+        <v>505726</v>
       </c>
       <c r="R4" t="n">
-        <v>6573177</v>
+        <v>6573245</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1016,33 +1012,19 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hack i död trädstam.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1060,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123280343</v>
+        <v>123280720</v>
       </c>
       <c r="B5" t="n">
-        <v>8434</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,36 +1054,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1112,7 +1097,7 @@
         <v>505723</v>
       </c>
       <c r="R5" t="n">
-        <v>6573156</v>
+        <v>6573415</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1160,26 +1145,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1197,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123280108</v>
+        <v>123280332</v>
       </c>
       <c r="B6" t="n">
-        <v>56697</v>
+        <v>57506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1209,25 +1174,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1235,7 +1200,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1245,10 +1210,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505744</v>
+        <v>505716</v>
       </c>
       <c r="R6" t="n">
-        <v>6573212</v>
+        <v>6573177</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1283,6 +1248,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska hack i död trädstam.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1291,6 +1261,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1307,10 +1292,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123280125</v>
+        <v>123280178</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1319,50 +1304,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505726</v>
+        <v>505688</v>
       </c>
       <c r="R7" t="n">
-        <v>6573245</v>
+        <v>6573291</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1410,6 +1390,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1430,7 +1430,7 @@
         <v>123280124</v>
       </c>
       <c r="B8" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123280304</v>
+        <v>123280343</v>
       </c>
       <c r="B9" t="n">
-        <v>39932</v>
+        <v>8436</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1578,25 +1578,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101166</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505683</v>
+        <v>505723</v>
       </c>
       <c r="R9" t="n">
-        <v>6573205</v>
+        <v>6573156</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1706,7 +1706,7 @@
         <v>123280204</v>
       </c>
       <c r="B10" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>123377883</v>
       </c>
       <c r="B11" t="n">
-        <v>58165</v>
+        <v>58168</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123374704</v>
+        <v>123372894</v>
       </c>
       <c r="B12" t="n">
-        <v>57487</v>
+        <v>57641</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1971,16 +1971,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103020</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1989,27 +1989,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505574</v>
+        <v>505631</v>
       </c>
       <c r="R12" t="n">
-        <v>6573159</v>
+        <v>6573031</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2038,7 +2035,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2048,12 +2045,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gamla ringhack i tall.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2068,26 +2060,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2098,17 +2070,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Per Arneborn, Camilla Berglund, Anneli Sjöstrand</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123372894</v>
+        <v>123374704</v>
       </c>
       <c r="B13" t="n">
-        <v>57638</v>
+        <v>57490</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2121,16 +2093,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103020</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2139,24 +2111,27 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505631</v>
+        <v>505574</v>
       </c>
       <c r="R13" t="n">
-        <v>6573031</v>
+        <v>6573159</v>
       </c>
       <c r="S13" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2185,7 +2160,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2195,7 +2170,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gamla ringhack i tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2210,6 +2190,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Arneborn, Anneli Sjöstrand, Camilla Berglund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2230,7 +2230,7 @@
         <v>123377543</v>
       </c>
       <c r="B14" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123280304</v>
+        <v>123280124</v>
       </c>
       <c r="B2" t="n">
-        <v>39935</v>
+        <v>91010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101166</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505683</v>
+        <v>505726</v>
       </c>
       <c r="R2" t="n">
-        <v>6573205</v>
+        <v>6573245</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,6 +764,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>4 tickor på samma tall.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,22 +786,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +814,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123280108</v>
+        <v>123280125</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,46 +826,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505744</v>
+        <v>505726</v>
       </c>
       <c r="R3" t="n">
-        <v>6573212</v>
+        <v>6573245</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -904,8 +910,14 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -922,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123280125</v>
+        <v>123280343</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>8436</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,50 +946,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505726</v>
+        <v>505723</v>
       </c>
       <c r="R4" t="n">
-        <v>6573245</v>
+        <v>6573156</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1025,6 +1034,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1042,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123280720</v>
+        <v>123280332</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,39 +1083,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1094,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505723</v>
+        <v>505716</v>
       </c>
       <c r="R5" t="n">
-        <v>6573415</v>
+        <v>6573177</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1132,19 +1157,33 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska hack i död trädstam.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1162,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123280332</v>
+        <v>123280720</v>
       </c>
       <c r="B6" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,35 +1213,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1210,10 +1253,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505716</v>
+        <v>505723</v>
       </c>
       <c r="R6" t="n">
-        <v>6573177</v>
+        <v>6573415</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1248,33 +1291,19 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska hack i död trädstam.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1292,10 +1321,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123280178</v>
+        <v>123280304</v>
       </c>
       <c r="B7" t="n">
-        <v>91008</v>
+        <v>39935</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1308,30 +1337,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>101166</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1339,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505688</v>
+        <v>505683</v>
       </c>
       <c r="R7" t="n">
-        <v>6573291</v>
+        <v>6573205</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1394,12 +1425,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1409,7 +1440,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1427,10 +1458,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123280124</v>
+        <v>123280108</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>56700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1439,49 +1470,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505726</v>
+        <v>505744</v>
       </c>
       <c r="R8" t="n">
-        <v>6573245</v>
+        <v>6573212</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1516,40 +1544,14 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>4 tickor på samma tall.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1566,10 +1568,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123280343</v>
+        <v>123280178</v>
       </c>
       <c r="B9" t="n">
-        <v>8436</v>
+        <v>91010</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1578,36 +1580,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505723</v>
+        <v>505688</v>
       </c>
       <c r="R9" t="n">
-        <v>6573156</v>
+        <v>6573291</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1706,7 +1706,7 @@
         <v>123280204</v>
       </c>
       <c r="B10" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>123377883</v>
       </c>
       <c r="B11" t="n">
-        <v>58168</v>
+        <v>58169</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123372894</v>
+        <v>123374704</v>
       </c>
       <c r="B12" t="n">
-        <v>57641</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1971,16 +1971,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103020</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1989,24 +1989,27 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505631</v>
+        <v>505574</v>
       </c>
       <c r="R12" t="n">
-        <v>6573031</v>
+        <v>6573159</v>
       </c>
       <c r="S12" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2035,7 +2038,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2045,7 +2048,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gamla ringhack i tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2060,6 +2068,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2070,17 +2098,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Arneborn, Camilla Berglund, Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123374704</v>
+        <v>123372894</v>
       </c>
       <c r="B13" t="n">
-        <v>57490</v>
+        <v>57642</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2093,16 +2121,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103020</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2111,27 +2139,24 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505574</v>
+        <v>505631</v>
       </c>
       <c r="R13" t="n">
-        <v>6573159</v>
+        <v>6573031</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2160,7 +2185,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2170,12 +2195,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gamla ringhack i tall.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2190,26 +2210,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Per Arneborn, Anneli Sjöstrand, Camilla Berglund</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2230,7 +2230,7 @@
         <v>123377543</v>
       </c>
       <c r="B14" t="n">
-        <v>91008</v>
+        <v>91010</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -814,10 +814,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123280125</v>
+        <v>123280343</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>8436</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,50 +826,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505726</v>
+        <v>505723</v>
       </c>
       <c r="R3" t="n">
-        <v>6573245</v>
+        <v>6573156</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -917,6 +914,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123280343</v>
+        <v>123280125</v>
       </c>
       <c r="B4" t="n">
-        <v>8436</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,47 +963,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505723</v>
+        <v>505726</v>
       </c>
       <c r="R4" t="n">
-        <v>6573156</v>
+        <v>6573245</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1034,26 +1054,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -814,10 +814,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123280343</v>
+        <v>123280125</v>
       </c>
       <c r="B3" t="n">
-        <v>8436</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,47 +826,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505723</v>
+        <v>505726</v>
       </c>
       <c r="R3" t="n">
-        <v>6573156</v>
+        <v>6573245</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -914,26 +917,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -951,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123280125</v>
+        <v>123280343</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>8436</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,50 +946,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505726</v>
+        <v>505723</v>
       </c>
       <c r="R4" t="n">
-        <v>6573245</v>
+        <v>6573156</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1054,6 +1034,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123280124</v>
+        <v>123280343</v>
       </c>
       <c r="B2" t="n">
-        <v>91010</v>
+        <v>8436</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505726</v>
+        <v>505723</v>
       </c>
       <c r="R2" t="n">
-        <v>6573245</v>
+        <v>6573156</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,11 +762,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>4 tickor på samma tall.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -786,17 +779,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123280125</v>
+        <v>123280108</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,50 +824,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505726</v>
+        <v>505744</v>
       </c>
       <c r="R3" t="n">
-        <v>6573245</v>
+        <v>6573212</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -910,14 +904,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -934,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123280343</v>
+        <v>123280720</v>
       </c>
       <c r="B4" t="n">
-        <v>8436</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,36 +934,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -986,7 +977,7 @@
         <v>505723</v>
       </c>
       <c r="R4" t="n">
-        <v>6573156</v>
+        <v>6573415</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1034,26 +1025,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123280332</v>
+        <v>123280178</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>91010</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,31 +1058,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1119,10 +1089,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505716</v>
+        <v>505688</v>
       </c>
       <c r="R5" t="n">
-        <v>6573177</v>
+        <v>6573291</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1157,17 +1127,13 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska hack i död trädstam.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1176,14 +1142,24 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1201,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123280720</v>
+        <v>123280124</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>91010</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1213,50 +1189,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505723</v>
+        <v>505726</v>
       </c>
       <c r="R6" t="n">
-        <v>6573415</v>
+        <v>6573245</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1291,6 +1266,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>4 tickor på samma tall.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1304,6 +1284,21 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1321,10 +1316,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123280304</v>
+        <v>123280125</v>
       </c>
       <c r="B7" t="n">
-        <v>39935</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1333,47 +1328,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101166</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505683</v>
+        <v>505726</v>
       </c>
       <c r="R7" t="n">
-        <v>6573205</v>
+        <v>6573245</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1421,26 +1419,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1458,10 +1436,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123280108</v>
+        <v>123280204</v>
       </c>
       <c r="B8" t="n">
-        <v>56700</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1470,25 +1448,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1496,7 +1474,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1506,10 +1484,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505744</v>
+        <v>505719</v>
       </c>
       <c r="R8" t="n">
-        <v>6573212</v>
+        <v>6573262</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1544,6 +1522,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska hack i död trädstam</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1552,6 +1535,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Dead tree stem</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1568,10 +1566,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123280178</v>
+        <v>123280332</v>
       </c>
       <c r="B9" t="n">
-        <v>91010</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1584,30 +1582,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1615,10 +1614,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505688</v>
+        <v>505716</v>
       </c>
       <c r="R9" t="n">
-        <v>6573291</v>
+        <v>6573177</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1653,13 +1652,17 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska hack i död trädstam.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1668,24 +1671,14 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1703,10 +1696,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123280204</v>
+        <v>123280304</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>39935</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1719,29 +1712,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>101166</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1751,10 +1745,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505719</v>
+        <v>505683</v>
       </c>
       <c r="R10" t="n">
-        <v>6573262</v>
+        <v>6573205</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1789,17 +1783,13 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska hack i död trädstam</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1808,14 +1798,24 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Död trädstam</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Dead tree stem</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123280343</v>
+        <v>123280720</v>
       </c>
       <c r="B2" t="n">
-        <v>8436</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,7 +730,7 @@
         <v>505723</v>
       </c>
       <c r="R2" t="n">
-        <v>6573156</v>
+        <v>6573415</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,26 +778,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123280108</v>
+        <v>123280178</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>91010</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,35 +807,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -860,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505744</v>
+        <v>505688</v>
       </c>
       <c r="R3" t="n">
-        <v>6573212</v>
+        <v>6573291</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -904,8 +886,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -922,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123280720</v>
+        <v>123280332</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,39 +942,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -974,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505723</v>
+        <v>505716</v>
       </c>
       <c r="R4" t="n">
-        <v>6573415</v>
+        <v>6573177</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1012,19 +1016,33 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hack i död trädstam.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1042,7 +1060,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123280178</v>
+        <v>123280124</v>
       </c>
       <c r="B5" t="n">
         <v>91010</v>
@@ -1077,22 +1095,26 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505688</v>
+        <v>505726</v>
       </c>
       <c r="R5" t="n">
-        <v>6573291</v>
+        <v>6573245</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1127,6 +1149,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4 tickor på samma tall.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1152,14 +1179,9 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1177,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123280124</v>
+        <v>123280108</v>
       </c>
       <c r="B6" t="n">
-        <v>91010</v>
+        <v>56700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,49 +1211,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505726</v>
+        <v>505744</v>
       </c>
       <c r="R6" t="n">
-        <v>6573245</v>
+        <v>6573212</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1266,40 +1285,14 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>4 tickor på samma tall.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1316,10 +1309,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123280125</v>
+        <v>123280204</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1328,50 +1321,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505726</v>
+        <v>505719</v>
       </c>
       <c r="R7" t="n">
-        <v>6573245</v>
+        <v>6573262</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1406,19 +1395,33 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska hack i död trädstam</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Dead tree stem</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1436,10 +1439,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123280204</v>
+        <v>123280125</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1448,46 +1451,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505719</v>
+        <v>505726</v>
       </c>
       <c r="R8" t="n">
-        <v>6573262</v>
+        <v>6573245</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1522,33 +1529,19 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska hack i död trädstam</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Dead tree stem</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1566,10 +1559,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123280332</v>
+        <v>123280304</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>39935</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1582,29 +1575,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>101166</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1614,10 +1608,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505716</v>
+        <v>505683</v>
       </c>
       <c r="R9" t="n">
-        <v>6573177</v>
+        <v>6573205</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1652,17 +1646,13 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska hack i död trädstam.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1671,14 +1661,24 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123280304</v>
+        <v>123280343</v>
       </c>
       <c r="B10" t="n">
-        <v>39935</v>
+        <v>8436</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1708,25 +1708,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101166</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505683</v>
+        <v>505723</v>
       </c>
       <c r="R10" t="n">
-        <v>6573205</v>
+        <v>6573156</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123280720</v>
+        <v>123280204</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505723</v>
+        <v>505719</v>
       </c>
       <c r="R2" t="n">
-        <v>6573415</v>
+        <v>6573262</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,19 +761,33 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hack i död trädstam</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead tree stem</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -795,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123280178</v>
+        <v>123280343</v>
       </c>
       <c r="B3" t="n">
-        <v>91010</v>
+        <v>8436</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +817,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505688</v>
+        <v>505723</v>
       </c>
       <c r="R3" t="n">
-        <v>6573291</v>
+        <v>6573156</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,12 +909,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -912,7 +924,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -930,10 +942,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123280332</v>
+        <v>123280124</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>91010</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,42 +958,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505716</v>
+        <v>505726</v>
       </c>
       <c r="R4" t="n">
-        <v>6573177</v>
+        <v>6573245</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1018,7 +1033,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska hack i död trädstam.</t>
+          <t>4 tickor på samma tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,6 +1042,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1035,14 +1051,19 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1060,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123280124</v>
+        <v>123280125</v>
       </c>
       <c r="B5" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,38 +1093,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1149,11 +1171,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>4 tickor på samma tall.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1167,21 +1184,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1199,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123280108</v>
+        <v>123280178</v>
       </c>
       <c r="B6" t="n">
-        <v>56700</v>
+        <v>91010</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,35 +1213,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1247,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505744</v>
+        <v>505688</v>
       </c>
       <c r="R6" t="n">
-        <v>6573212</v>
+        <v>6573291</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1291,8 +1292,34 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1309,10 +1336,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123280204</v>
+        <v>123280720</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,35 +1348,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1357,10 +1388,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505719</v>
+        <v>505723</v>
       </c>
       <c r="R7" t="n">
-        <v>6573262</v>
+        <v>6573415</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1395,33 +1426,19 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska hack i död trädstam</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Dead tree stem</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1439,10 +1456,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123280125</v>
+        <v>123280332</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1451,50 +1468,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505726</v>
+        <v>505716</v>
       </c>
       <c r="R8" t="n">
-        <v>6573245</v>
+        <v>6573177</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1529,19 +1542,33 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska hack i död trädstam.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1696,10 +1723,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123280343</v>
+        <v>123280108</v>
       </c>
       <c r="B10" t="n">
-        <v>8436</v>
+        <v>56700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1712,30 +1739,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1745,10 +1771,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505723</v>
+        <v>505744</v>
       </c>
       <c r="R10" t="n">
-        <v>6573156</v>
+        <v>6573212</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1789,34 +1815,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1833,10 +1833,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123377883</v>
+        <v>123374704</v>
       </c>
       <c r="B11" t="n">
-        <v>58169</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1845,20 +1845,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103044</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1867,24 +1867,27 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505503</v>
+        <v>505574</v>
       </c>
       <c r="R11" t="n">
-        <v>6572768</v>
+        <v>6573159</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1913,7 +1916,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1923,7 +1926,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gamla ringhack i tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1938,6 +1946,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1948,17 +1976,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Arneborn, Camilla Berglund, Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123374704</v>
+        <v>123372894</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>57642</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1971,16 +1999,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103020</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1989,27 +2017,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505574</v>
+        <v>505631</v>
       </c>
       <c r="R12" t="n">
-        <v>6573159</v>
+        <v>6573031</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2038,7 +2063,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2048,12 +2073,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gamla ringhack i tall.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2068,26 +2088,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2098,17 +2098,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Per Arneborn, Camilla Berglund, Anneli Sjöstrand</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123372894</v>
+        <v>123377883</v>
       </c>
       <c r="B13" t="n">
-        <v>57642</v>
+        <v>58169</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103020</v>
+        <v>103044</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2150,13 +2150,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505631</v>
+        <v>505503</v>
       </c>
       <c r="R13" t="n">
-        <v>6573031</v>
+        <v>6572768</v>
       </c>
       <c r="S13" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123280343</v>
+        <v>123280332</v>
       </c>
       <c r="B3" t="n">
-        <v>8436</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,34 +817,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -854,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505723</v>
+        <v>505716</v>
       </c>
       <c r="R3" t="n">
-        <v>6573156</v>
+        <v>6573177</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,13 +891,17 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hack i död trädstam.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,24 +910,14 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -942,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123280124</v>
+        <v>123280304</v>
       </c>
       <c r="B4" t="n">
-        <v>91010</v>
+        <v>39935</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,45 +951,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>101166</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Uggle stenar, Nrk</t>
+          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505726</v>
+        <v>505683</v>
       </c>
       <c r="R4" t="n">
-        <v>6573245</v>
+        <v>6573205</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1031,11 +1022,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>4 tickor på samma tall.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1053,17 +1039,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1081,10 +1072,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123280125</v>
+        <v>123280124</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1093,39 +1084,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1171,6 +1161,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4 tickor på samma tall.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1184,6 +1179,21 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1201,10 +1211,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123280178</v>
+        <v>123280343</v>
       </c>
       <c r="B6" t="n">
-        <v>91010</v>
+        <v>8436</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1213,34 +1223,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1248,10 +1260,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505688</v>
+        <v>505723</v>
       </c>
       <c r="R6" t="n">
-        <v>6573291</v>
+        <v>6573156</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1303,12 +1315,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1318,7 +1330,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1336,7 +1348,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123280720</v>
+        <v>123280125</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1384,14 +1396,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
+          <t>Uggle stenar, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505723</v>
+        <v>505726</v>
       </c>
       <c r="R7" t="n">
-        <v>6573415</v>
+        <v>6573245</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1456,10 +1468,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123280332</v>
+        <v>123280720</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1468,35 +1480,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1504,10 +1520,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505716</v>
+        <v>505723</v>
       </c>
       <c r="R8" t="n">
-        <v>6573177</v>
+        <v>6573415</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1542,33 +1558,19 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska hack i död trädstam.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1586,10 +1588,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123280304</v>
+        <v>123280178</v>
       </c>
       <c r="B9" t="n">
-        <v>39935</v>
+        <v>91010</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1602,32 +1604,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101166</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505683</v>
+        <v>505688</v>
       </c>
       <c r="R9" t="n">
-        <v>6573205</v>
+        <v>6573291</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123374704</v>
+        <v>123377883</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>58169</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1845,20 +1845,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1867,27 +1867,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505574</v>
+        <v>505503</v>
       </c>
       <c r="R11" t="n">
-        <v>6573159</v>
+        <v>6572768</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1916,7 +1913,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1926,12 +1923,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gamla ringhack i tall.</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1946,26 +1938,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1976,17 +1948,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Per Arneborn, Camilla Berglund, Anneli Sjöstrand</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123372894</v>
+        <v>123374704</v>
       </c>
       <c r="B12" t="n">
-        <v>57642</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1999,16 +1971,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103020</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2017,24 +1989,27 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Uggle stenar, Mellringe grusgrop, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505631</v>
+        <v>505574</v>
       </c>
       <c r="R12" t="n">
-        <v>6573031</v>
+        <v>6573159</v>
       </c>
       <c r="S12" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2063,7 +2038,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2073,7 +2048,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gamla ringhack i tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2088,6 +2068,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2098,17 +2098,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Arneborn, Camilla Berglund, Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123377883</v>
+        <v>123372894</v>
       </c>
       <c r="B13" t="n">
-        <v>58169</v>
+        <v>57642</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2150,13 +2150,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505503</v>
+        <v>505631</v>
       </c>
       <c r="R13" t="n">
-        <v>6572768</v>
+        <v>6573031</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -2376,7 +2376,7 @@
         <v>123218995</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -2376,7 +2376,7 @@
         <v>123218995</v>
       </c>
       <c r="B15" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 10992-2025 artfynd.xlsx
+++ b/artfynd/A 10992-2025 artfynd.xlsx
@@ -2376,7 +2376,7 @@
         <v>123218995</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
